--- a/data/btc_price_fred.xlsx
+++ b/data/btc_price_fred.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4213"/>
+  <dimension ref="A1:C4280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55197,9 +55197,880 @@
         <v>46220</v>
       </c>
       <c r="B4213" t="n">
-        <v>63965.390625</v>
+        <v>63900.18</v>
       </c>
       <c r="C4213" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4214">
+      <c r="A4214" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B4214" t="n">
+        <v>64793.76</v>
+      </c>
+      <c r="C4214" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4215">
+      <c r="A4215" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B4215" t="n">
+        <v>64571.18</v>
+      </c>
+      <c r="C4215" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4216">
+      <c r="A4216" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B4216" t="n">
+        <v>65151.3</v>
+      </c>
+      <c r="C4216" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4217">
+      <c r="A4217" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B4217" t="n">
+        <v>66553.73</v>
+      </c>
+      <c r="C4217" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4218">
+      <c r="A4218" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B4218" t="n">
+        <v>66063.67</v>
+      </c>
+      <c r="C4218" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4219">
+      <c r="A4219" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B4219" t="n">
+        <v>65000.99</v>
+      </c>
+      <c r="C4219" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4220">
+      <c r="A4220" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B4220" t="n">
+        <v>64108.38</v>
+      </c>
+      <c r="C4220" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4221">
+      <c r="A4221" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B4221" t="n">
+        <v>64319.9</v>
+      </c>
+      <c r="C4221" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4222">
+      <c r="A4222" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B4222" t="n">
+        <v>65243.31</v>
+      </c>
+      <c r="C4222" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4223">
+      <c r="A4223" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4223" t="n">
+        <v>63692.68</v>
+      </c>
+      <c r="C4223" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4224">
+      <c r="A4224" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B4224" t="n">
+        <v>63945.6</v>
+      </c>
+      <c r="C4224" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4225">
+      <c r="A4225" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4225" t="n">
+        <v>63896.15</v>
+      </c>
+      <c r="C4225" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4226">
+      <c r="A4226" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4226" t="n">
+        <v>64817.71</v>
+      </c>
+      <c r="C4226" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4227">
+      <c r="A4227" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4227" t="n">
+        <v>62886.64</v>
+      </c>
+      <c r="C4227" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4228">
+      <c r="A4228" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B4228" t="n">
+        <v>62835</v>
+      </c>
+      <c r="C4228" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4229">
+      <c r="A4229" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B4229" t="n">
+        <v>63443.93</v>
+      </c>
+      <c r="C4229" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4230">
+      <c r="A4230" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4230" t="n">
+        <v>63503.04</v>
+      </c>
+      <c r="C4230" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4231">
+      <c r="A4231" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B4231" t="n">
+        <v>64023.39</v>
+      </c>
+      <c r="C4231" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4232">
+      <c r="A4232" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4232" t="n">
+        <v>64555.45</v>
+      </c>
+      <c r="C4232" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4233">
+      <c r="A4233" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4233" t="n">
+        <v>64291.84</v>
+      </c>
+      <c r="C4233" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4234">
+      <c r="A4234" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B4234" t="n">
+        <v>64877.34</v>
+      </c>
+      <c r="C4234" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4235">
+      <c r="A4235" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B4235" t="n">
+        <v>64910.12</v>
+      </c>
+      <c r="C4235" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4236">
+      <c r="A4236" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B4236" t="n">
+        <v>64855.5</v>
+      </c>
+      <c r="C4236" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4237">
+      <c r="A4237" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B4237" t="n">
+        <v>63876.26</v>
+      </c>
+      <c r="C4237" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4238">
+      <c r="A4238" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4238" t="n">
+        <v>63528.48</v>
+      </c>
+      <c r="C4238" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4239">
+      <c r="A4239" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4239" t="n">
+        <v>63402.49</v>
+      </c>
+      <c r="C4239" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4240">
+      <c r="A4240" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4240" t="n">
+        <v>63387.81</v>
+      </c>
+      <c r="C4240" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4241">
+      <c r="A4241" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B4241" t="n">
+        <v>62968.43</v>
+      </c>
+      <c r="C4241" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4242">
+      <c r="A4242" s="2" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B4242" t="n">
+        <v>62999.01</v>
+      </c>
+      <c r="C4242" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4243">
+      <c r="A4243" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B4243" t="n">
+        <v>62859.47</v>
+      </c>
+      <c r="C4243" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4244">
+      <c r="A4244" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B4244" t="n">
+        <v>64423.92</v>
+      </c>
+      <c r="C4244" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4245">
+      <c r="A4245" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B4245" t="n">
+        <v>64625.4</v>
+      </c>
+      <c r="C4245" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4246">
+      <c r="A4246" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4246" t="n">
+        <v>69487.60000000001</v>
+      </c>
+      <c r="C4246" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4247">
+      <c r="A4247" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B4247" t="n">
+        <v>73086.97</v>
+      </c>
+      <c r="C4247" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4248">
+      <c r="A4248" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4248" t="n">
+        <v>78126.63</v>
+      </c>
+      <c r="C4248" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" s="2" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B4249" t="n">
+        <v>77117.73</v>
+      </c>
+      <c r="C4249" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" s="2" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B4250" t="n">
+        <v>77637.69</v>
+      </c>
+      <c r="C4250" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B4251" t="n">
+        <v>78981.39</v>
+      </c>
+      <c r="C4251" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B4252" t="n">
+        <v>78510.95</v>
+      </c>
+      <c r="C4252" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4253">
+      <c r="A4253" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4253" t="n">
+        <v>78961.92999999999</v>
+      </c>
+      <c r="C4253" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4254">
+      <c r="A4254" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B4254" t="n">
+        <v>80209.61</v>
+      </c>
+      <c r="C4254" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4255">
+      <c r="A4255" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B4255" t="n">
+        <v>77838.64999999999</v>
+      </c>
+      <c r="C4255" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4256">
+      <c r="A4256" s="2" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B4256" t="n">
+        <v>78215</v>
+      </c>
+      <c r="C4256" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4257">
+      <c r="A4257" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B4257" t="n">
+        <v>77757.98</v>
+      </c>
+      <c r="C4257" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4258">
+      <c r="A4258" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B4258" t="n">
+        <v>78603.02</v>
+      </c>
+      <c r="C4258" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4259">
+      <c r="A4259" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4259" t="n">
+        <v>77392.64999999999</v>
+      </c>
+      <c r="C4259" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4260">
+      <c r="A4260" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B4260" t="n">
+        <v>77330.23</v>
+      </c>
+      <c r="C4260" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4261">
+      <c r="A4261" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B4261" t="n">
+        <v>81129.19</v>
+      </c>
+      <c r="C4261" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4262" t="n">
+        <v>79658.55</v>
+      </c>
+      <c r="C4262" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B4263" t="n">
+        <v>79879.24000000001</v>
+      </c>
+      <c r="C4263" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B4264" t="n">
+        <v>80309.06</v>
+      </c>
+      <c r="C4264" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B4265" t="n">
+        <v>79067.23</v>
+      </c>
+      <c r="C4265" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B4266" t="n">
+        <v>78548.91</v>
+      </c>
+      <c r="C4266" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4267" t="n">
+        <v>78303.59</v>
+      </c>
+      <c r="C4267" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B4268" t="n">
+        <v>76664.89</v>
+      </c>
+      <c r="C4268" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4269">
+      <c r="A4269" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4269" t="n">
+        <v>77276.5</v>
+      </c>
+      <c r="C4269" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4270">
+      <c r="A4270" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B4270" t="n">
+        <v>77270.73</v>
+      </c>
+      <c r="C4270" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B4271" t="n">
+        <v>76804.92</v>
+      </c>
+      <c r="C4271" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4272">
+      <c r="A4272" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B4272" t="n">
+        <v>78200.38</v>
+      </c>
+      <c r="C4272" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4273" t="n">
+        <v>75656.09</v>
+      </c>
+      <c r="C4273" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4274" t="n">
+        <v>76208.64</v>
+      </c>
+      <c r="C4274" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4275" t="n">
+        <v>76366.39999999999</v>
+      </c>
+      <c r="C4275" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4276" t="n">
+        <v>80844</v>
+      </c>
+      <c r="C4276" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B4277" t="n">
+        <v>81186</v>
+      </c>
+      <c r="C4277" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B4278" t="n">
+        <v>81253.37</v>
+      </c>
+      <c r="C4278" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4279" t="n">
+        <v>86396.74000000001</v>
+      </c>
+      <c r="C4279" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4280" t="n">
+        <v>85938.03125</v>
+      </c>
+      <c r="C4280" t="inlineStr">
         <is>
           <t>yahoo_fallback</t>
         </is>

--- a/data/btc_price_fred.xlsx
+++ b/data/btc_price_fred.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4280"/>
+  <dimension ref="A1:C4289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56068,9 +56068,126 @@
         <v>46287</v>
       </c>
       <c r="B4280" t="n">
-        <v>85938.03125</v>
+        <v>86249.98</v>
       </c>
       <c r="C4280" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4281" t="n">
+        <v>84452.97</v>
+      </c>
+      <c r="C4281" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4282" t="n">
+        <v>84470.75999999999</v>
+      </c>
+      <c r="C4282" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4283" t="n">
+        <v>84048.07000000001</v>
+      </c>
+      <c r="C4283" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B4284" t="n">
+        <v>84337.36</v>
+      </c>
+      <c r="C4284" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B4285" t="n">
+        <v>84553.91</v>
+      </c>
+      <c r="C4285" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4286" t="n">
+        <v>83487.03</v>
+      </c>
+      <c r="C4286" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4287" t="n">
+        <v>83636.7</v>
+      </c>
+      <c r="C4287" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4288" t="n">
+        <v>83482.50999999999</v>
+      </c>
+      <c r="C4288" t="inlineStr">
+        <is>
+          <t>fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4289" t="n">
+        <v>83788.078125</v>
+      </c>
+      <c r="C4289" t="inlineStr">
         <is>
           <t>yahoo_fallback</t>
         </is>
